--- a/artfynd/A 41415-2024 artfynd.xlsx
+++ b/artfynd/A 41415-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ33"/>
+  <dimension ref="A1:AZ40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1453,10 +1453,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121004574</v>
+        <v>136674360</v>
       </c>
       <c r="B9" t="n">
-        <v>93189</v>
+        <v>87494</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,21 +1464,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4361</v>
+        <v>1988</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1487,17 +1487,17 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Lappbrännbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>550601</v>
+        <v>550523</v>
       </c>
       <c r="R9" t="n">
-        <v>6994490</v>
+        <v>6994411</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1521,12 +1521,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1553,38 +1553,38 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004574</t>
+          <t>https://artportalen.se/Sighting/136674360</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121004572</v>
+        <v>136673577</v>
       </c>
       <c r="B10" t="n">
-        <v>93197</v>
+        <v>93416</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1593,17 +1593,17 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog norr om Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>550483</v>
+        <v>550453</v>
       </c>
       <c r="R10" t="n">
-        <v>6994428</v>
+        <v>6994607</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1627,12 +1627,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1659,38 +1659,38 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004572</t>
+          <t>https://artportalen.se/Sighting/136673577</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121004577</v>
+        <v>136673646</v>
       </c>
       <c r="B11" t="n">
-        <v>93197</v>
+        <v>93416</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1699,17 +1699,17 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog norr om Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>550574</v>
+        <v>550429</v>
       </c>
       <c r="R11" t="n">
-        <v>6994485</v>
+        <v>6994500</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1765,16 +1765,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004577</t>
+          <t>https://artportalen.se/Sighting/136673646</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121004580</v>
+        <v>121004574</v>
       </c>
       <c r="B12" t="n">
-        <v>93197</v>
+        <v>93189</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1782,21 +1782,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1809,10 +1809,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>550446</v>
+        <v>550601</v>
       </c>
       <c r="R12" t="n">
-        <v>6994540</v>
+        <v>6994490</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1871,13 +1871,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004580</t>
+          <t>https://artportalen.se/Sighting/121004574</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126098379</v>
+        <v>121004572</v>
       </c>
       <c r="B13" t="n">
         <v>93197</v>
@@ -1911,14 +1911,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550364</v>
+        <v>550483</v>
       </c>
       <c r="R13" t="n">
-        <v>6994541</v>
+        <v>6994428</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1945,17 +1945,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Förra årets fruktkroppar</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1982,13 +1977,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126098379</t>
+          <t>https://artportalen.se/Sighting/121004572</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126098889</v>
+        <v>121004577</v>
       </c>
       <c r="B14" t="n">
         <v>93197</v>
@@ -2022,14 +2017,14 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550414</v>
+        <v>550574</v>
       </c>
       <c r="R14" t="n">
-        <v>6994562</v>
+        <v>6994485</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2056,17 +2051,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Förra årets fruktkroppar</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2093,16 +2083,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126098889</t>
+          <t>https://artportalen.se/Sighting/121004577</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134246409</v>
+        <v>121004580</v>
       </c>
       <c r="B15" t="n">
-        <v>93271</v>
+        <v>93197</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2128,19 +2118,22 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lapprännbäcken, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550472</v>
+        <v>550446</v>
       </c>
       <c r="R15" t="n">
-        <v>6994595</v>
+        <v>6994540</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2164,12 +2157,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2178,55 +2171,56 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246409</t>
+          <t>https://artportalen.se/Sighting/121004580</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121004576</v>
+        <v>126098379</v>
       </c>
       <c r="B16" t="n">
-        <v>79327</v>
+        <v>93197</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2235,14 +2229,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550574</v>
+        <v>550364</v>
       </c>
       <c r="R16" t="n">
-        <v>6994485</v>
+        <v>6994541</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2269,12 +2263,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Förra årets fruktkroppar</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2301,38 +2300,38 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004576</t>
+          <t>https://artportalen.se/Sighting/126098379</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121004579</v>
+        <v>126098889</v>
       </c>
       <c r="B17" t="n">
-        <v>79327</v>
+        <v>93197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2341,14 +2340,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550553</v>
+        <v>550414</v>
       </c>
       <c r="R17" t="n">
-        <v>6994537</v>
+        <v>6994562</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2375,12 +2374,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Förra årets fruktkroppar</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2407,38 +2411,38 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004579</t>
+          <t>https://artportalen.se/Sighting/126098889</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134246413</v>
+        <v>134246409</v>
       </c>
       <c r="B18" t="n">
-        <v>79373</v>
+        <v>93271</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2448,10 +2452,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>550559</v>
+        <v>550472</v>
       </c>
       <c r="R18" t="n">
-        <v>6994526</v>
+        <v>6994595</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2509,16 +2513,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246413</t>
+          <t>https://artportalen.se/Sighting/134246409</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>103996050</v>
+        <v>136626251</v>
       </c>
       <c r="B19" t="n">
-        <v>83307</v>
+        <v>93400</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2526,34 +2530,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Svartabbortjärnen, Jmt</t>
+          <t>Skog norr om Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>550561</v>
+        <v>550513</v>
       </c>
       <c r="R19" t="n">
-        <v>6994584</v>
+        <v>6994449</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2580,22 +2584,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>14:58</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>14:58</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2606,11 +2600,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AS19" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2620,26 +2609,22 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103996050</t>
+          <t>https://artportalen.se/Sighting/136626251</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134246407</v>
+        <v>136673649</v>
       </c>
       <c r="B20" t="n">
-        <v>79130</v>
+        <v>93400</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2647,34 +2632,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lapprännbäcken, Jmt</t>
+          <t>Skog norr om Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>550434</v>
+        <v>550429</v>
       </c>
       <c r="R20" t="n">
-        <v>6994476</v>
+        <v>6994500</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2701,12 +2689,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2715,33 +2703,34 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246407</t>
+          <t>https://artportalen.se/Sighting/136673649</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>103996058</v>
+        <v>136673613</v>
       </c>
       <c r="B21" t="n">
-        <v>79946</v>
+        <v>93412</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2749,34 +2738,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>4366</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Svartabbortjärnen, Jmt</t>
+          <t>Skog norr om Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>550472</v>
+        <v>550415</v>
       </c>
       <c r="R21" t="n">
-        <v>6994541</v>
+        <v>6994553</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2803,22 +2795,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>14:54</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>14:54</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2827,13 +2809,9 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AS21" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2843,48 +2821,44 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103996058</t>
+          <t>https://artportalen.se/Sighting/136673613</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126099190</v>
+        <v>121004576</v>
       </c>
       <c r="B22" t="n">
-        <v>80432</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2893,14 +2867,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>550528</v>
+        <v>550574</v>
       </c>
       <c r="R22" t="n">
-        <v>6994556</v>
+        <v>6994485</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2927,17 +2901,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2964,54 +2933,57 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126099190</t>
+          <t>https://artportalen.se/Sighting/121004576</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134246412</v>
+        <v>121004579</v>
       </c>
       <c r="B23" t="n">
-        <v>80488</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lapprännbäcken, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>550551</v>
+        <v>550553</v>
       </c>
       <c r="R23" t="n">
-        <v>6994539</v>
+        <v>6994537</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3035,12 +3007,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3049,55 +3021,56 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246412</t>
+          <t>https://artportalen.se/Sighting/121004579</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134246411</v>
+        <v>134246413</v>
       </c>
       <c r="B24" t="n">
-        <v>80492</v>
+        <v>79373</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3107,10 +3080,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>550551</v>
+        <v>550559</v>
       </c>
       <c r="R24" t="n">
-        <v>6994539</v>
+        <v>6994526</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3168,57 +3141,54 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246411</t>
+          <t>https://artportalen.se/Sighting/134246413</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126098507</v>
+        <v>103996050</v>
       </c>
       <c r="B25" t="n">
-        <v>80467</v>
+        <v>83307</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6463</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
+          <t>Svartabbortjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>550359</v>
+        <v>550561</v>
       </c>
       <c r="R25" t="n">
-        <v>6994564</v>
+        <v>6994584</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3242,17 +3212,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På asp</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3261,9 +3236,13 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3273,22 +3252,26 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126098507</t>
+          <t>https://artportalen.se/Sighting/103996050</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>62025586</v>
+        <v>134246407</v>
       </c>
       <c r="B26" t="n">
-        <v>5495</v>
+        <v>79130</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3296,34 +3279,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>101410</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hoberget, Jmt</t>
+          <t>Lapprännbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>550466</v>
+        <v>550434</v>
       </c>
       <c r="R26" t="n">
-        <v>6994615</v>
+        <v>6994476</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3350,12 +3333,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2016-07-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2016-07-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3366,83 +3349,69 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Gammal tall</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62025586</t>
+          <t>https://artportalen.se/Sighting/134246407</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126098329</v>
+        <v>103996058</v>
       </c>
       <c r="B27" t="n">
-        <v>99118</v>
+        <v>79946</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
+          <t>Svartabbortjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>550325</v>
+        <v>550472</v>
       </c>
       <c r="R27" t="n">
-        <v>6994462</v>
+        <v>6994541</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3466,17 +3435,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Rik förekomst vid björkhögstubbe</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3485,9 +3459,13 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3497,50 +3475,53 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126098329</t>
+          <t>https://artportalen.se/Sighting/103996058</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126098423</v>
+        <v>126099190</v>
       </c>
       <c r="B28" t="n">
-        <v>99118</v>
+        <v>80432</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3548,10 +3529,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>550359</v>
+        <v>550528</v>
       </c>
       <c r="R28" t="n">
-        <v>6994564</v>
+        <v>6994556</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3586,6 +3567,11 @@
           <t>2025-06-19</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3610,58 +3596,54 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126098423</t>
+          <t>https://artportalen.se/Sighting/126099190</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126098335</v>
+        <v>134246412</v>
       </c>
       <c r="B29" t="n">
-        <v>99140</v>
+        <v>80488</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
+          <t>Lapprännbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550326</v>
+        <v>550551</v>
       </c>
       <c r="R29" t="n">
-        <v>6994473</v>
+        <v>6994539</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3685,12 +3667,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3699,69 +3681,68 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126098335</t>
+          <t>https://artportalen.se/Sighting/134246412</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>103996049</v>
+        <v>134246411</v>
       </c>
       <c r="B30" t="n">
-        <v>79085</v>
+        <v>80492</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6461</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Svartabbortjärnen, Jmt</t>
+          <t>Lapprännbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550474</v>
+        <v>550551</v>
       </c>
       <c r="R30" t="n">
-        <v>6994542</v>
+        <v>6994539</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3788,22 +3769,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>14:55</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>14:55</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3814,62 +3785,53 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AS30" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103996049</t>
+          <t>https://artportalen.se/Sighting/134246411</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126098363</v>
+        <v>126098507</v>
       </c>
       <c r="B31" t="n">
-        <v>79085</v>
+        <v>80467</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>6463</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3882,10 +3844,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>550365</v>
+        <v>550359</v>
       </c>
       <c r="R31" t="n">
-        <v>6994523</v>
+        <v>6994564</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3920,6 +3882,11 @@
           <t>2025-06-19</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På asp</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -3944,16 +3911,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126098363</t>
+          <t>https://artportalen.se/Sighting/126098507</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134246410</v>
+        <v>62025586</v>
       </c>
       <c r="B32" t="n">
-        <v>79131</v>
+        <v>5495</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3961,34 +3928,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>101410</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lapprännbäcken, Jmt</t>
+          <t>Hoberget, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550482</v>
+        <v>550466</v>
       </c>
       <c r="R32" t="n">
-        <v>6994611</v>
+        <v>6994615</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4015,12 +3982,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2016-07-06</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2016-07-06</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4031,58 +3998,69 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Gammal tall</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246410</t>
+          <t>https://artportalen.se/Sighting/62025586</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126098483</v>
+        <v>126098329</v>
       </c>
       <c r="B33" t="n">
-        <v>80392</v>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4090,10 +4068,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550359</v>
+        <v>550325</v>
       </c>
       <c r="R33" t="n">
-        <v>6994564</v>
+        <v>6994462</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4130,7 +4108,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>Rik förekomst vid björkhögstubbe</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4157,7 +4135,763 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/126098329</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>126098423</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>550359</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6994564</v>
+      </c>
+      <c r="S34" t="n">
+        <v>25</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126098423</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>126098335</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>550326</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6994473</v>
+      </c>
+      <c r="S35" t="n">
+        <v>25</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126098335</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>103996049</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Svartabbortjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>550474</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6994542</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS36" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103996049</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>126098363</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>550365</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6994523</v>
+      </c>
+      <c r="S37" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126098363</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>134246410</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Lapprännbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>550482</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6994611</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246410</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>126098483</v>
+      </c>
+      <c r="B39" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>550359</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6994564</v>
+      </c>
+      <c r="S39" t="n">
+        <v>25</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På asp</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/126098483</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>136674417</v>
+      </c>
+      <c r="B40" t="n">
+        <v>93414</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6047725</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Rödfläckig zontaggsvamp</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Skog vid Lappbrännbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>550558</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6994443</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136674417</t>
         </is>
       </c>
     </row>
@@ -4195,6 +4929,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41415-2024 artfynd.xlsx
+++ b/artfynd/A 41415-2024 artfynd.xlsx
@@ -1456,7 +1456,7 @@
         <v>136674360</v>
       </c>
       <c r="B9" t="n">
-        <v>87494</v>
+        <v>87496</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>136673577</v>
       </c>
       <c r="B10" t="n">
-        <v>93416</v>
+        <v>93419</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>136673646</v>
       </c>
       <c r="B11" t="n">
-        <v>93416</v>
+        <v>93419</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>136626251</v>
       </c>
       <c r="B19" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>136673649</v>
       </c>
       <c r="B20" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>136673613</v>
       </c>
       <c r="B21" t="n">
-        <v>93412</v>
+        <v>93415</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>136674417</v>
       </c>
       <c r="B40" t="n">
-        <v>93414</v>
+        <v>93417</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 41415-2024 artfynd.xlsx
+++ b/artfynd/A 41415-2024 artfynd.xlsx
@@ -1562,7 +1562,7 @@
         <v>136673577</v>
       </c>
       <c r="B10" t="n">
-        <v>93419</v>
+        <v>93420</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>136673646</v>
       </c>
       <c r="B11" t="n">
-        <v>93419</v>
+        <v>93420</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>136626251</v>
       </c>
       <c r="B19" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>136673649</v>
       </c>
       <c r="B20" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>136673613</v>
       </c>
       <c r="B21" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>136674417</v>
       </c>
       <c r="B40" t="n">
-        <v>93417</v>
+        <v>93418</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 41415-2024 artfynd.xlsx
+++ b/artfynd/A 41415-2024 artfynd.xlsx
@@ -1456,7 +1456,7 @@
         <v>136674360</v>
       </c>
       <c r="B9" t="n">
-        <v>87496</v>
+        <v>87498</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>136673577</v>
       </c>
       <c r="B10" t="n">
-        <v>93420</v>
+        <v>93425</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>136673646</v>
       </c>
       <c r="B11" t="n">
-        <v>93420</v>
+        <v>93425</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>136626251</v>
       </c>
       <c r="B19" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>136673649</v>
       </c>
       <c r="B20" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>136673613</v>
       </c>
       <c r="B21" t="n">
-        <v>93416</v>
+        <v>93421</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>136674417</v>
       </c>
       <c r="B40" t="n">
-        <v>93418</v>
+        <v>93423</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 41415-2024 artfynd.xlsx
+++ b/artfynd/A 41415-2024 artfynd.xlsx
@@ -1456,7 +1456,7 @@
         <v>136674360</v>
       </c>
       <c r="B9" t="n">
-        <v>87498</v>
+        <v>87500</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>136673577</v>
       </c>
       <c r="B10" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>136673646</v>
       </c>
       <c r="B11" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>136626251</v>
       </c>
       <c r="B19" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>136673649</v>
       </c>
       <c r="B20" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>136673613</v>
       </c>
       <c r="B21" t="n">
-        <v>93421</v>
+        <v>93423</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>136674417</v>
       </c>
       <c r="B40" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 41415-2024 artfynd.xlsx
+++ b/artfynd/A 41415-2024 artfynd.xlsx
@@ -1456,7 +1456,7 @@
         <v>136674360</v>
       </c>
       <c r="B9" t="n">
-        <v>87500</v>
+        <v>87502</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>136673577</v>
       </c>
       <c r="B10" t="n">
-        <v>93427</v>
+        <v>93429</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>136673646</v>
       </c>
       <c r="B11" t="n">
-        <v>93427</v>
+        <v>93429</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>136626251</v>
       </c>
       <c r="B19" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>136673649</v>
       </c>
       <c r="B20" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>136673613</v>
       </c>
       <c r="B21" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>136674417</v>
       </c>
       <c r="B40" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 41415-2024 artfynd.xlsx
+++ b/artfynd/A 41415-2024 artfynd.xlsx
@@ -1456,7 +1456,7 @@
         <v>136674360</v>
       </c>
       <c r="B9" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>136673577</v>
       </c>
       <c r="B10" t="n">
-        <v>93429</v>
+        <v>93431</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>136673646</v>
       </c>
       <c r="B11" t="n">
-        <v>93429</v>
+        <v>93431</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>136626251</v>
       </c>
       <c r="B19" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>136673649</v>
       </c>
       <c r="B20" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>136673613</v>
       </c>
       <c r="B21" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>136674417</v>
       </c>
       <c r="B40" t="n">
-        <v>93427</v>
+        <v>93429</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 41415-2024 artfynd.xlsx
+++ b/artfynd/A 41415-2024 artfynd.xlsx
@@ -1456,7 +1456,7 @@
         <v>136674360</v>
       </c>
       <c r="B9" t="n">
-        <v>87504</v>
+        <v>87505</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>136673577</v>
       </c>
       <c r="B10" t="n">
-        <v>93431</v>
+        <v>93432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>136673646</v>
       </c>
       <c r="B11" t="n">
-        <v>93431</v>
+        <v>93432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>136626251</v>
       </c>
       <c r="B19" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>136673649</v>
       </c>
       <c r="B20" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>136673613</v>
       </c>
       <c r="B21" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>136674417</v>
       </c>
       <c r="B40" t="n">
-        <v>93429</v>
+        <v>93430</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 41415-2024 artfynd.xlsx
+++ b/artfynd/A 41415-2024 artfynd.xlsx
@@ -1456,7 +1456,7 @@
         <v>136674360</v>
       </c>
       <c r="B9" t="n">
-        <v>87505</v>
+        <v>87511</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>136673577</v>
       </c>
       <c r="B10" t="n">
-        <v>93432</v>
+        <v>93438</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>136673646</v>
       </c>
       <c r="B11" t="n">
-        <v>93432</v>
+        <v>93438</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>136626251</v>
       </c>
       <c r="B19" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>136673649</v>
       </c>
       <c r="B20" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>136673613</v>
       </c>
       <c r="B21" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>136674417</v>
       </c>
       <c r="B40" t="n">
-        <v>93430</v>
+        <v>93436</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 41415-2024 artfynd.xlsx
+++ b/artfynd/A 41415-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ40"/>
+  <dimension ref="A1:AZ41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,32 +680,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126098914</v>
+        <v>137163120</v>
       </c>
       <c r="B2" t="n">
-        <v>83302</v>
+        <v>92374</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>310</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -714,17 +714,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
+          <t>Skog norr om Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>550461</v>
+        <v>550426</v>
       </c>
       <c r="R2" t="n">
-        <v>6994538</v>
+        <v>6994512</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,29 +748,44 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På tallåga</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>vanlig tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Undersidan av tallåga.</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris var. sylvestris # Undersidan av tallåga.</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -785,16 +800,16 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126098914</t>
+          <t>https://artportalen.se/Sighting/137163120</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>62025587</v>
+        <v>126098914</v>
       </c>
       <c r="B3" t="n">
-        <v>78993</v>
+        <v>83302</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,37 +817,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>310</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hoberget, Jmt</t>
+          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>550466</v>
+        <v>550461</v>
       </c>
       <c r="R3" t="n">
-        <v>6994615</v>
+        <v>6994538</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -856,12 +874,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2016-07-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2016-07-06</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På tallåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -870,40 +893,31 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Grov tallåga</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62025587</t>
+          <t>https://artportalen.se/Sighting/126098914</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103996101</v>
+        <v>62025587</v>
       </c>
       <c r="B4" t="n">
         <v>78993</v>
@@ -934,14 +948,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Svartabbortjärnen, Jmt</t>
+          <t>Hoberget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>550466</v>
       </c>
       <c r="R4" t="n">
-        <v>6994537</v>
+        <v>6994615</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,22 +982,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:53</t>
+          <t>2016-07-06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:53</t>
+          <t>2016-07-06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,36 +999,37 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Grov tallåga</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103996101</t>
+          <t>https://artportalen.se/Sighting/62025587</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126098349</v>
+        <v>103996101</v>
       </c>
       <c r="B5" t="n">
         <v>78993</v>
@@ -1053,22 +1058,19 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
+          <t>Svartabbortjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>550332</v>
+        <v>550466</v>
       </c>
       <c r="R5" t="n">
-        <v>6994514</v>
+        <v>6994537</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1092,17 +1094,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På grov tallåga</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,9 +1118,13 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1123,22 +1134,26 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126098349</t>
+          <t>https://artportalen.se/Sighting/103996101</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126098314</v>
+        <v>126098349</v>
       </c>
       <c r="B6" t="n">
-        <v>83173</v>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1146,21 +1161,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,10 +1188,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>550342</v>
+        <v>550332</v>
       </c>
       <c r="R6" t="n">
-        <v>6994466</v>
+        <v>6994514</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1211,6 +1226,11 @@
           <t>2025-06-19</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På grov tallåga</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1235,38 +1255,38 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126098314</t>
+          <t>https://artportalen.se/Sighting/126098349</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126152097</v>
+        <v>126098314</v>
       </c>
       <c r="B7" t="n">
-        <v>92083</v>
+        <v>83173</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1503</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1279,10 +1299,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>550473</v>
+        <v>550342</v>
       </c>
       <c r="R7" t="n">
-        <v>6994545</v>
+        <v>6994466</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1341,38 +1361,38 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126152097</t>
+          <t>https://artportalen.se/Sighting/126098314</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121004582</v>
+        <v>126152097</v>
       </c>
       <c r="B8" t="n">
-        <v>90932</v>
+        <v>92083</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1962</v>
+        <v>1503</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1381,14 +1401,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550413</v>
+        <v>550473</v>
       </c>
       <c r="R8" t="n">
-        <v>6994537</v>
+        <v>6994545</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1415,12 +1435,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,16 +1467,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004582</t>
+          <t>https://artportalen.se/Sighting/126152097</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136674360</v>
+        <v>121004582</v>
       </c>
       <c r="B9" t="n">
-        <v>87511</v>
+        <v>90932</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,21 +1484,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1988</v>
+        <v>1962</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1487,17 +1507,17 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skog vid Lappbrännbäcken, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>550523</v>
+        <v>550413</v>
       </c>
       <c r="R9" t="n">
-        <v>6994411</v>
+        <v>6994537</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1521,12 +1541,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1553,38 +1573,38 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136674360</t>
+          <t>https://artportalen.se/Sighting/121004582</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136673577</v>
+        <v>136674360</v>
       </c>
       <c r="B10" t="n">
-        <v>93438</v>
+        <v>87515</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2059</v>
+        <v>1988</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1593,14 +1613,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skog norr om Blomkindtjärnen, Jmt</t>
+          <t>Skog vid Lappbrännbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>550453</v>
+        <v>550523</v>
       </c>
       <c r="R10" t="n">
-        <v>6994607</v>
+        <v>6994411</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1659,16 +1679,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136673577</t>
+          <t>https://artportalen.se/Sighting/136674360</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136673646</v>
+        <v>136673577</v>
       </c>
       <c r="B11" t="n">
-        <v>93438</v>
+        <v>93442</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>550429</v>
+        <v>550453</v>
       </c>
       <c r="R11" t="n">
-        <v>6994500</v>
+        <v>6994607</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1765,38 +1785,38 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136673646</t>
+          <t>https://artportalen.se/Sighting/136673577</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121004574</v>
+        <v>136673646</v>
       </c>
       <c r="B12" t="n">
-        <v>93189</v>
+        <v>93442</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1805,17 +1825,17 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog norr om Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>550601</v>
+        <v>550429</v>
       </c>
       <c r="R12" t="n">
-        <v>6994490</v>
+        <v>6994500</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1839,12 +1859,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1871,16 +1891,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004574</t>
+          <t>https://artportalen.se/Sighting/136673646</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121004572</v>
+        <v>121004574</v>
       </c>
       <c r="B13" t="n">
-        <v>93197</v>
+        <v>93189</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1888,21 +1908,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1915,10 +1935,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550483</v>
+        <v>550601</v>
       </c>
       <c r="R13" t="n">
-        <v>6994428</v>
+        <v>6994490</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1977,13 +1997,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004572</t>
+          <t>https://artportalen.se/Sighting/121004574</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121004577</v>
+        <v>121004572</v>
       </c>
       <c r="B14" t="n">
         <v>93197</v>
@@ -2021,10 +2041,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550574</v>
+        <v>550483</v>
       </c>
       <c r="R14" t="n">
-        <v>6994485</v>
+        <v>6994428</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2083,13 +2103,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004577</t>
+          <t>https://artportalen.se/Sighting/121004572</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121004580</v>
+        <v>121004577</v>
       </c>
       <c r="B15" t="n">
         <v>93197</v>
@@ -2127,10 +2147,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550446</v>
+        <v>550574</v>
       </c>
       <c r="R15" t="n">
-        <v>6994540</v>
+        <v>6994485</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2189,13 +2209,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004580</t>
+          <t>https://artportalen.se/Sighting/121004577</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126098379</v>
+        <v>121004580</v>
       </c>
       <c r="B16" t="n">
         <v>93197</v>
@@ -2229,14 +2249,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550364</v>
+        <v>550446</v>
       </c>
       <c r="R16" t="n">
-        <v>6994541</v>
+        <v>6994540</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2263,17 +2283,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Förra årets fruktkroppar</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2300,13 +2315,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126098379</t>
+          <t>https://artportalen.se/Sighting/121004580</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126098889</v>
+        <v>126098379</v>
       </c>
       <c r="B17" t="n">
         <v>93197</v>
@@ -2344,10 +2359,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550414</v>
+        <v>550364</v>
       </c>
       <c r="R17" t="n">
-        <v>6994562</v>
+        <v>6994541</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2411,16 +2426,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126098889</t>
+          <t>https://artportalen.se/Sighting/126098379</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134246409</v>
+        <v>126098889</v>
       </c>
       <c r="B18" t="n">
-        <v>93271</v>
+        <v>93197</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2446,19 +2461,22 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lapprännbäcken, Jmt</t>
+          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>550472</v>
+        <v>550414</v>
       </c>
       <c r="R18" t="n">
-        <v>6994595</v>
+        <v>6994562</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2482,12 +2500,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Förra årets fruktkroppar</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2496,33 +2519,34 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246409</t>
+          <t>https://artportalen.se/Sighting/126098889</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>136626251</v>
+        <v>134246409</v>
       </c>
       <c r="B19" t="n">
-        <v>93422</v>
+        <v>93271</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2550,14 +2574,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skog norr om Blomkindtjärnen, Jmt</t>
+          <t>Lapprännbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>550513</v>
+        <v>550472</v>
       </c>
       <c r="R19" t="n">
-        <v>6994449</v>
+        <v>6994595</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2584,12 +2608,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2604,27 +2628,27 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136626251</t>
+          <t>https://artportalen.se/Sighting/134246409</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>136673649</v>
+        <v>136626251</v>
       </c>
       <c r="B20" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2650,19 +2674,16 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skog norr om Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>550429</v>
+        <v>550513</v>
       </c>
       <c r="R20" t="n">
-        <v>6994500</v>
+        <v>6994449</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2703,7 +2724,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2721,16 +2741,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136673649</t>
+          <t>https://artportalen.se/Sighting/136626251</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>136673613</v>
+        <v>136673649</v>
       </c>
       <c r="B21" t="n">
-        <v>93434</v>
+        <v>93426</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2738,21 +2758,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2765,10 +2785,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>550415</v>
+        <v>550429</v>
       </c>
       <c r="R21" t="n">
-        <v>6994553</v>
+        <v>6994500</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2827,38 +2847,38 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136673613</t>
+          <t>https://artportalen.se/Sighting/136673649</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121004576</v>
+        <v>136673613</v>
       </c>
       <c r="B22" t="n">
-        <v>79327</v>
+        <v>93438</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2867,17 +2887,17 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog norr om Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>550574</v>
+        <v>550415</v>
       </c>
       <c r="R22" t="n">
-        <v>6994485</v>
+        <v>6994553</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2901,12 +2921,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2933,13 +2953,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004576</t>
+          <t>https://artportalen.se/Sighting/136673613</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121004579</v>
+        <v>121004576</v>
       </c>
       <c r="B23" t="n">
         <v>79327</v>
@@ -2977,10 +2997,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>550553</v>
+        <v>550574</v>
       </c>
       <c r="R23" t="n">
-        <v>6994537</v>
+        <v>6994485</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3039,16 +3059,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004579</t>
+          <t>https://artportalen.se/Sighting/121004576</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134246413</v>
+        <v>121004579</v>
       </c>
       <c r="B24" t="n">
-        <v>79373</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3074,19 +3094,22 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lapprännbäcken, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>550559</v>
+        <v>550553</v>
       </c>
       <c r="R24" t="n">
-        <v>6994526</v>
+        <v>6994537</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3110,12 +3133,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3124,68 +3147,69 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246413</t>
+          <t>https://artportalen.se/Sighting/121004579</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>103996050</v>
+        <v>134246413</v>
       </c>
       <c r="B25" t="n">
-        <v>83307</v>
+        <v>79373</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Svartabbortjärnen, Jmt</t>
+          <t>Lapprännbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>550561</v>
+        <v>550559</v>
       </c>
       <c r="R25" t="n">
-        <v>6994584</v>
+        <v>6994526</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3212,22 +3236,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>14:58</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>14:58</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3238,40 +3252,31 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AS25" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103996050</t>
+          <t>https://artportalen.se/Sighting/134246413</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134246407</v>
+        <v>103996050</v>
       </c>
       <c r="B26" t="n">
-        <v>79130</v>
+        <v>83307</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3279,34 +3284,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lapprännbäcken, Jmt</t>
+          <t>Svartabbortjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>550434</v>
+        <v>550561</v>
       </c>
       <c r="R26" t="n">
-        <v>6994476</v>
+        <v>6994584</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3333,12 +3338,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3349,31 +3364,40 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AS26" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246407</t>
+          <t>https://artportalen.se/Sighting/103996050</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>103996058</v>
+        <v>134246407</v>
       </c>
       <c r="B27" t="n">
-        <v>79946</v>
+        <v>79130</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3381,34 +3405,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Svartabbortjärnen, Jmt</t>
+          <t>Lapprännbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>550472</v>
+        <v>550434</v>
       </c>
       <c r="R27" t="n">
-        <v>6994541</v>
+        <v>6994476</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3435,22 +3459,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>14:54</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>14:54</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3461,40 +3475,31 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AS27" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103996058</t>
+          <t>https://artportalen.se/Sighting/134246407</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126099190</v>
+        <v>103996058</v>
       </c>
       <c r="B28" t="n">
-        <v>80432</v>
+        <v>79946</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3502,40 +3507,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
+          <t>Svartabbortjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>550528</v>
+        <v>550472</v>
       </c>
       <c r="R28" t="n">
-        <v>6994556</v>
+        <v>6994541</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3559,17 +3561,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3578,9 +3585,13 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AS28" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3590,22 +3601,26 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126099190</t>
+          <t>https://artportalen.se/Sighting/103996058</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134246412</v>
+        <v>126099190</v>
       </c>
       <c r="B29" t="n">
-        <v>80488</v>
+        <v>80432</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3631,19 +3646,22 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lapprännbäcken, Jmt</t>
+          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550551</v>
+        <v>550528</v>
       </c>
       <c r="R29" t="n">
-        <v>6994539</v>
+        <v>6994556</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3667,12 +3685,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3681,55 +3704,56 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246412</t>
+          <t>https://artportalen.se/Sighting/126099190</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134246411</v>
+        <v>134246412</v>
       </c>
       <c r="B30" t="n">
-        <v>80492</v>
+        <v>80488</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3800,16 +3824,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246411</t>
+          <t>https://artportalen.se/Sighting/134246412</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126098507</v>
+        <v>134246411</v>
       </c>
       <c r="B31" t="n">
-        <v>80467</v>
+        <v>80492</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3817,40 +3841,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6463</v>
+        <v>6461</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
+          <t>Lapprännbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>550359</v>
+        <v>550551</v>
       </c>
       <c r="R31" t="n">
-        <v>6994564</v>
+        <v>6994539</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3874,17 +3895,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På asp</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3893,72 +3909,74 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126098507</t>
+          <t>https://artportalen.se/Sighting/134246411</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>62025586</v>
+        <v>126098507</v>
       </c>
       <c r="B32" t="n">
-        <v>5495</v>
+        <v>80467</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>101410</v>
+        <v>6463</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Hoberget, Jmt</t>
+          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550466</v>
+        <v>550359</v>
       </c>
       <c r="R32" t="n">
-        <v>6994615</v>
+        <v>6994564</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3982,12 +4000,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2016-07-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2016-07-06</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3996,85 +4019,72 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Gammal tall</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62025586</t>
+          <t>https://artportalen.se/Sighting/126098507</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126098329</v>
+        <v>62025586</v>
       </c>
       <c r="B33" t="n">
-        <v>99118</v>
+        <v>5495</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>101410</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
+          <t>Hoberget, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550325</v>
+        <v>550466</v>
       </c>
       <c r="R33" t="n">
-        <v>6994462</v>
+        <v>6994615</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4098,17 +4108,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2016-07-06</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Rik förekomst vid björkhögstubbe</t>
+          <t>2016-07-06</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4117,31 +4122,40 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Gammal tall</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126098329</t>
+          <t>https://artportalen.se/Sighting/62025586</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126098423</v>
+        <v>126098329</v>
       </c>
       <c r="B34" t="n">
         <v>99118</v>
@@ -4180,10 +4194,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550359</v>
+        <v>550325</v>
       </c>
       <c r="R34" t="n">
-        <v>6994564</v>
+        <v>6994462</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4218,6 +4232,11 @@
           <t>2025-06-19</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Rik förekomst vid björkhögstubbe</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4242,38 +4261,38 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126098423</t>
+          <t>https://artportalen.se/Sighting/126098329</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126098335</v>
+        <v>126098423</v>
       </c>
       <c r="B35" t="n">
-        <v>99140</v>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4287,10 +4306,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>550326</v>
+        <v>550359</v>
       </c>
       <c r="R35" t="n">
-        <v>6994473</v>
+        <v>6994564</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4349,54 +4368,58 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126098335</t>
+          <t>https://artportalen.se/Sighting/126098423</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>103996049</v>
+        <v>126098335</v>
       </c>
       <c r="B36" t="n">
-        <v>79085</v>
+        <v>99140</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>221952</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Svartabbortjärnen, Jmt</t>
+          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>550474</v>
+        <v>550326</v>
       </c>
       <c r="R36" t="n">
-        <v>6994542</v>
+        <v>6994473</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4420,22 +4443,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>14:55</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>14:55</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4444,13 +4457,9 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AS36" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4460,23 +4469,19 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103996049</t>
+          <t>https://artportalen.se/Sighting/126098335</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126098363</v>
+        <v>103996049</v>
       </c>
       <c r="B37" t="n">
         <v>79085</v>
@@ -4505,22 +4510,19 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
+          <t>Svartabbortjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>550365</v>
+        <v>550474</v>
       </c>
       <c r="R37" t="n">
-        <v>6994523</v>
+        <v>6994542</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4544,12 +4546,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4558,9 +4570,13 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AS37" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4570,22 +4586,26 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126098363</t>
+          <t>https://artportalen.se/Sighting/103996049</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134246410</v>
+        <v>126098363</v>
       </c>
       <c r="B38" t="n">
-        <v>79131</v>
+        <v>79085</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4611,19 +4631,22 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lapprännbäcken, Jmt</t>
+          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>550482</v>
+        <v>550365</v>
       </c>
       <c r="R38" t="n">
-        <v>6994611</v>
+        <v>6994523</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4647,12 +4670,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4661,74 +4684,72 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246410</t>
+          <t>https://artportalen.se/Sighting/126098363</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126098483</v>
+        <v>134246410</v>
       </c>
       <c r="B39" t="n">
-        <v>80392</v>
+        <v>79131</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229497</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
+          <t>Lapprännbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>550359</v>
+        <v>550482</v>
       </c>
       <c r="R39" t="n">
-        <v>6994564</v>
+        <v>6994611</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4752,17 +4773,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På asp</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4771,71 +4787,74 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126098483</t>
+          <t>https://artportalen.se/Sighting/134246410</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>136674417</v>
+        <v>126098483</v>
       </c>
       <c r="B40" t="n">
-        <v>93436</v>
+        <v>80392</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6047725</v>
+        <v>229497</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Skog vid Lappbrännbäcken, Jmt</t>
+          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>550558</v>
+        <v>550359</v>
       </c>
       <c r="R40" t="n">
-        <v>6994443</v>
+        <v>6994564</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4859,12 +4878,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4890,6 +4914,108 @@
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126098483</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>136674417</v>
+      </c>
+      <c r="B41" t="n">
+        <v>93440</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6047725</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Rödfläckig zontaggsvamp</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Skog vid Lappbrännbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>550558</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6994443</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136674417</t>
         </is>
@@ -4936,6 +5062,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41415-2024 artfynd.xlsx
+++ b/artfynd/A 41415-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ41"/>
+  <dimension ref="A1:AZ40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,32 +680,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>137163120</v>
+        <v>126098914</v>
       </c>
       <c r="B2" t="n">
-        <v>92374</v>
+        <v>83302</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>65</v>
+        <v>310</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -714,17 +714,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skog norr om Blomkindtjärnen, Jmt</t>
+          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>550426</v>
+        <v>550461</v>
       </c>
       <c r="R2" t="n">
-        <v>6994512</v>
+        <v>6994538</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,44 +748,29 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På tallåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>vanlig tall</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris var. sylvestris</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>Undersidan av tallåga.</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris var. sylvestris # Undersidan av tallåga.</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -800,16 +785,16 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137163120</t>
+          <t>https://artportalen.se/Sighting/126098914</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126098914</v>
+        <v>62025587</v>
       </c>
       <c r="B3" t="n">
-        <v>83302</v>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,40 +802,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>310</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
+          <t>Hoberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>550461</v>
+        <v>550466</v>
       </c>
       <c r="R3" t="n">
-        <v>6994538</v>
+        <v>6994615</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,17 +856,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2016-07-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På tallåga</t>
+          <t>2016-07-06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,31 +870,40 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Grov tallåga</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126098914</t>
+          <t>https://artportalen.se/Sighting/62025587</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>62025587</v>
+        <v>103996101</v>
       </c>
       <c r="B4" t="n">
         <v>78993</v>
@@ -948,14 +934,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hoberget, Jmt</t>
+          <t>Svartabbortjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>550466</v>
       </c>
       <c r="R4" t="n">
-        <v>6994615</v>
+        <v>6994537</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,12 +968,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2016-07-06</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2016-07-06</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,37 +995,36 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Grov tallåga</t>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62025587</t>
+          <t>https://artportalen.se/Sighting/103996101</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103996101</v>
+        <v>126098349</v>
       </c>
       <c r="B5" t="n">
         <v>78993</v>
@@ -1058,19 +1053,22 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svartabbortjärnen, Jmt</t>
+          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>550466</v>
+        <v>550332</v>
       </c>
       <c r="R5" t="n">
-        <v>6994537</v>
+        <v>6994514</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1094,22 +1092,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:53</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:53</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På grov tallåga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,13 +1111,9 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1134,26 +1123,22 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103996101</t>
+          <t>https://artportalen.se/Sighting/126098349</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126098349</v>
+        <v>126098314</v>
       </c>
       <c r="B6" t="n">
-        <v>78993</v>
+        <v>83173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1161,21 +1146,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1188,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>550332</v>
+        <v>550342</v>
       </c>
       <c r="R6" t="n">
-        <v>6994514</v>
+        <v>6994466</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1226,11 +1211,6 @@
           <t>2025-06-19</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På grov tallåga</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1255,38 +1235,38 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126098349</t>
+          <t>https://artportalen.se/Sighting/126098314</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126098314</v>
+        <v>126152097</v>
       </c>
       <c r="B7" t="n">
-        <v>83173</v>
+        <v>92083</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>1503</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1299,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>550342</v>
+        <v>550473</v>
       </c>
       <c r="R7" t="n">
-        <v>6994466</v>
+        <v>6994545</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1361,38 +1341,38 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126098314</t>
+          <t>https://artportalen.se/Sighting/126152097</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126152097</v>
+        <v>121004582</v>
       </c>
       <c r="B8" t="n">
-        <v>92083</v>
+        <v>90932</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1503</v>
+        <v>1962</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1401,14 +1381,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550473</v>
+        <v>550413</v>
       </c>
       <c r="R8" t="n">
-        <v>6994545</v>
+        <v>6994537</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1435,12 +1415,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,16 +1447,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126152097</t>
+          <t>https://artportalen.se/Sighting/121004582</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121004582</v>
+        <v>136674360</v>
       </c>
       <c r="B9" t="n">
-        <v>90932</v>
+        <v>87515</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,21 +1464,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1962</v>
+        <v>1988</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1507,17 +1487,17 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Lappbrännbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>550413</v>
+        <v>550523</v>
       </c>
       <c r="R9" t="n">
-        <v>6994537</v>
+        <v>6994411</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1541,12 +1521,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1573,38 +1553,38 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004582</t>
+          <t>https://artportalen.se/Sighting/136674360</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136674360</v>
+        <v>136673577</v>
       </c>
       <c r="B10" t="n">
-        <v>87515</v>
+        <v>93442</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1988</v>
+        <v>2059</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1613,14 +1593,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skog vid Lappbrännbäcken, Jmt</t>
+          <t>Skog norr om Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>550523</v>
+        <v>550453</v>
       </c>
       <c r="R10" t="n">
-        <v>6994411</v>
+        <v>6994607</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1679,13 +1659,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136674360</t>
+          <t>https://artportalen.se/Sighting/136673577</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136673577</v>
+        <v>136673646</v>
       </c>
       <c r="B11" t="n">
         <v>93442</v>
@@ -1723,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>550453</v>
+        <v>550429</v>
       </c>
       <c r="R11" t="n">
-        <v>6994607</v>
+        <v>6994500</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,38 +1765,38 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136673577</t>
+          <t>https://artportalen.se/Sighting/136673646</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136673646</v>
+        <v>121004574</v>
       </c>
       <c r="B12" t="n">
-        <v>93442</v>
+        <v>93189</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1825,17 +1805,17 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Skog norr om Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>550429</v>
+        <v>550601</v>
       </c>
       <c r="R12" t="n">
-        <v>6994500</v>
+        <v>6994490</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1859,12 +1839,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1891,16 +1871,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136673646</t>
+          <t>https://artportalen.se/Sighting/121004574</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121004574</v>
+        <v>121004572</v>
       </c>
       <c r="B13" t="n">
-        <v>93189</v>
+        <v>93197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1908,21 +1888,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1935,10 +1915,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550601</v>
+        <v>550483</v>
       </c>
       <c r="R13" t="n">
-        <v>6994490</v>
+        <v>6994428</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1997,13 +1977,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004574</t>
+          <t>https://artportalen.se/Sighting/121004572</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121004572</v>
+        <v>121004577</v>
       </c>
       <c r="B14" t="n">
         <v>93197</v>
@@ -2041,10 +2021,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550483</v>
+        <v>550574</v>
       </c>
       <c r="R14" t="n">
-        <v>6994428</v>
+        <v>6994485</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2103,13 +2083,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004572</t>
+          <t>https://artportalen.se/Sighting/121004577</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121004577</v>
+        <v>121004580</v>
       </c>
       <c r="B15" t="n">
         <v>93197</v>
@@ -2147,10 +2127,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550574</v>
+        <v>550446</v>
       </c>
       <c r="R15" t="n">
-        <v>6994485</v>
+        <v>6994540</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2209,13 +2189,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004577</t>
+          <t>https://artportalen.se/Sighting/121004580</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121004580</v>
+        <v>126098379</v>
       </c>
       <c r="B16" t="n">
         <v>93197</v>
@@ -2249,14 +2229,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550446</v>
+        <v>550364</v>
       </c>
       <c r="R16" t="n">
-        <v>6994540</v>
+        <v>6994541</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2283,12 +2263,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Förra årets fruktkroppar</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2315,13 +2300,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004580</t>
+          <t>https://artportalen.se/Sighting/126098379</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126098379</v>
+        <v>126098889</v>
       </c>
       <c r="B17" t="n">
         <v>93197</v>
@@ -2359,10 +2344,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550364</v>
+        <v>550414</v>
       </c>
       <c r="R17" t="n">
-        <v>6994541</v>
+        <v>6994562</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2426,16 +2411,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126098379</t>
+          <t>https://artportalen.se/Sighting/126098889</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126098889</v>
+        <v>134246409</v>
       </c>
       <c r="B18" t="n">
-        <v>93197</v>
+        <v>93271</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2461,22 +2446,19 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
+          <t>Lapprännbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>550414</v>
+        <v>550472</v>
       </c>
       <c r="R18" t="n">
-        <v>6994562</v>
+        <v>6994595</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2500,17 +2482,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Förra årets fruktkroppar</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2519,34 +2496,33 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126098889</t>
+          <t>https://artportalen.se/Sighting/134246409</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134246409</v>
+        <v>136626251</v>
       </c>
       <c r="B19" t="n">
-        <v>93271</v>
+        <v>93426</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2574,14 +2550,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lapprännbäcken, Jmt</t>
+          <t>Skog norr om Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>550472</v>
+        <v>550513</v>
       </c>
       <c r="R19" t="n">
-        <v>6994595</v>
+        <v>6994449</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2608,12 +2584,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2628,24 +2604,24 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246409</t>
+          <t>https://artportalen.se/Sighting/136626251</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>136626251</v>
+        <v>136673649</v>
       </c>
       <c r="B20" t="n">
         <v>93426</v>
@@ -2674,16 +2650,19 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skog norr om Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>550513</v>
+        <v>550429</v>
       </c>
       <c r="R20" t="n">
-        <v>6994449</v>
+        <v>6994500</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2724,6 +2703,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2741,16 +2721,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136626251</t>
+          <t>https://artportalen.se/Sighting/136673649</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>136673649</v>
+        <v>136673613</v>
       </c>
       <c r="B21" t="n">
-        <v>93426</v>
+        <v>93438</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2758,21 +2738,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2785,10 +2765,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>550429</v>
+        <v>550415</v>
       </c>
       <c r="R21" t="n">
-        <v>6994500</v>
+        <v>6994553</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2847,38 +2827,38 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136673649</t>
+          <t>https://artportalen.se/Sighting/136673613</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>136673613</v>
+        <v>121004576</v>
       </c>
       <c r="B22" t="n">
-        <v>93438</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2887,17 +2867,17 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Skog norr om Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>550415</v>
+        <v>550574</v>
       </c>
       <c r="R22" t="n">
-        <v>6994553</v>
+        <v>6994485</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2921,12 +2901,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2953,13 +2933,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136673613</t>
+          <t>https://artportalen.se/Sighting/121004576</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121004576</v>
+        <v>121004579</v>
       </c>
       <c r="B23" t="n">
         <v>79327</v>
@@ -2997,10 +2977,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>550574</v>
+        <v>550553</v>
       </c>
       <c r="R23" t="n">
-        <v>6994485</v>
+        <v>6994537</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3059,16 +3039,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004576</t>
+          <t>https://artportalen.se/Sighting/121004579</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121004579</v>
+        <v>134246413</v>
       </c>
       <c r="B24" t="n">
-        <v>79327</v>
+        <v>79373</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3094,22 +3074,19 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Lapprännbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>550553</v>
+        <v>550559</v>
       </c>
       <c r="R24" t="n">
-        <v>6994537</v>
+        <v>6994526</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3133,12 +3110,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3147,69 +3124,68 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004579</t>
+          <t>https://artportalen.se/Sighting/134246413</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134246413</v>
+        <v>103996050</v>
       </c>
       <c r="B25" t="n">
-        <v>79373</v>
+        <v>83307</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lapprännbäcken, Jmt</t>
+          <t>Svartabbortjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>550559</v>
+        <v>550561</v>
       </c>
       <c r="R25" t="n">
-        <v>6994526</v>
+        <v>6994584</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3236,12 +3212,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3252,31 +3238,40 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246413</t>
+          <t>https://artportalen.se/Sighting/103996050</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>103996050</v>
+        <v>134246407</v>
       </c>
       <c r="B26" t="n">
-        <v>83307</v>
+        <v>79130</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3284,34 +3279,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Svartabbortjärnen, Jmt</t>
+          <t>Lapprännbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>550561</v>
+        <v>550434</v>
       </c>
       <c r="R26" t="n">
-        <v>6994584</v>
+        <v>6994476</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3338,22 +3333,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>14:58</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>14:58</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3364,40 +3349,31 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AS26" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103996050</t>
+          <t>https://artportalen.se/Sighting/134246407</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134246407</v>
+        <v>103996058</v>
       </c>
       <c r="B27" t="n">
-        <v>79130</v>
+        <v>79946</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3405,34 +3381,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lapprännbäcken, Jmt</t>
+          <t>Svartabbortjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>550434</v>
+        <v>550472</v>
       </c>
       <c r="R27" t="n">
-        <v>6994476</v>
+        <v>6994541</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3459,12 +3435,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3475,31 +3461,40 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246407</t>
+          <t>https://artportalen.se/Sighting/103996058</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>103996058</v>
+        <v>126099190</v>
       </c>
       <c r="B28" t="n">
-        <v>79946</v>
+        <v>80432</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3507,37 +3502,40 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Svartabbortjärnen, Jmt</t>
+          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>550472</v>
+        <v>550528</v>
       </c>
       <c r="R28" t="n">
-        <v>6994541</v>
+        <v>6994556</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3561,22 +3559,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>14:54</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>14:54</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3585,13 +3578,9 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AS28" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3601,26 +3590,22 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103996058</t>
+          <t>https://artportalen.se/Sighting/126099190</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126099190</v>
+        <v>134246412</v>
       </c>
       <c r="B29" t="n">
-        <v>80432</v>
+        <v>80488</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3646,22 +3631,19 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
+          <t>Lapprännbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550528</v>
+        <v>550551</v>
       </c>
       <c r="R29" t="n">
-        <v>6994556</v>
+        <v>6994539</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3685,17 +3667,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3704,56 +3681,55 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126099190</t>
+          <t>https://artportalen.se/Sighting/134246412</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134246412</v>
+        <v>134246411</v>
       </c>
       <c r="B30" t="n">
-        <v>80488</v>
+        <v>80492</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3824,16 +3800,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246412</t>
+          <t>https://artportalen.se/Sighting/134246411</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134246411</v>
+        <v>126098507</v>
       </c>
       <c r="B31" t="n">
-        <v>80492</v>
+        <v>80467</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3841,37 +3817,40 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6461</v>
+        <v>6463</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lapprännbäcken, Jmt</t>
+          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>550551</v>
+        <v>550359</v>
       </c>
       <c r="R31" t="n">
-        <v>6994539</v>
+        <v>6994564</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3895,12 +3874,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3909,74 +3893,72 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246411</t>
+          <t>https://artportalen.se/Sighting/126098507</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126098507</v>
+        <v>62025586</v>
       </c>
       <c r="B32" t="n">
-        <v>80467</v>
+        <v>5495</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6463</v>
+        <v>101410</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
+          <t>Hoberget, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550359</v>
+        <v>550466</v>
       </c>
       <c r="R32" t="n">
-        <v>6994564</v>
+        <v>6994615</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4000,17 +3982,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2016-07-06</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På asp</t>
+          <t>2016-07-06</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4019,72 +3996,85 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Gammal tall</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126098507</t>
+          <t>https://artportalen.se/Sighting/62025586</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>62025586</v>
+        <v>126098329</v>
       </c>
       <c r="B33" t="n">
-        <v>5495</v>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>101410</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Hoberget, Jmt</t>
+          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550466</v>
+        <v>550325</v>
       </c>
       <c r="R33" t="n">
-        <v>6994615</v>
+        <v>6994462</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4108,12 +4098,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2016-07-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2016-07-06</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Rik förekomst vid björkhögstubbe</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4122,40 +4117,31 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Gammal tall</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62025586</t>
+          <t>https://artportalen.se/Sighting/126098329</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126098329</v>
+        <v>126098423</v>
       </c>
       <c r="B34" t="n">
         <v>99118</v>
@@ -4194,10 +4180,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550325</v>
+        <v>550359</v>
       </c>
       <c r="R34" t="n">
-        <v>6994462</v>
+        <v>6994564</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4232,11 +4218,6 @@
           <t>2025-06-19</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Rik förekomst vid björkhögstubbe</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4261,38 +4242,38 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126098329</t>
+          <t>https://artportalen.se/Sighting/126098423</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126098423</v>
+        <v>126098335</v>
       </c>
       <c r="B35" t="n">
-        <v>99118</v>
+        <v>99140</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4306,10 +4287,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>550359</v>
+        <v>550326</v>
       </c>
       <c r="R35" t="n">
-        <v>6994564</v>
+        <v>6994473</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4368,58 +4349,54 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126098423</t>
+          <t>https://artportalen.se/Sighting/126098335</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126098335</v>
+        <v>103996049</v>
       </c>
       <c r="B36" t="n">
-        <v>99140</v>
+        <v>79085</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221952</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
+          <t>Svartabbortjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>550326</v>
+        <v>550474</v>
       </c>
       <c r="R36" t="n">
-        <v>6994473</v>
+        <v>6994542</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4443,12 +4420,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4457,9 +4444,13 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AS36" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4469,19 +4460,23 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126098335</t>
+          <t>https://artportalen.se/Sighting/103996049</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>103996049</v>
+        <v>126098363</v>
       </c>
       <c r="B37" t="n">
         <v>79085</v>
@@ -4510,19 +4505,22 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Svartabbortjärnen, Jmt</t>
+          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>550474</v>
+        <v>550365</v>
       </c>
       <c r="R37" t="n">
-        <v>6994542</v>
+        <v>6994523</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4546,22 +4544,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>14:55</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>14:55</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4570,13 +4558,9 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AS37" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4586,26 +4570,22 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103996049</t>
+          <t>https://artportalen.se/Sighting/126098363</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126098363</v>
+        <v>134246410</v>
       </c>
       <c r="B38" t="n">
-        <v>79085</v>
+        <v>79131</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4631,22 +4611,19 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
+          <t>Lapprännbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>550365</v>
+        <v>550482</v>
       </c>
       <c r="R38" t="n">
-        <v>6994523</v>
+        <v>6994611</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4670,12 +4647,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4684,72 +4661,74 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126098363</t>
+          <t>https://artportalen.se/Sighting/134246410</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134246410</v>
+        <v>126098483</v>
       </c>
       <c r="B39" t="n">
-        <v>79131</v>
+        <v>80392</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>229497</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lapprännbäcken, Jmt</t>
+          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>550482</v>
+        <v>550359</v>
       </c>
       <c r="R39" t="n">
-        <v>6994611</v>
+        <v>6994564</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4773,12 +4752,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4787,74 +4771,71 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246410</t>
+          <t>https://artportalen.se/Sighting/126098483</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126098483</v>
+        <v>136674417</v>
       </c>
       <c r="B40" t="n">
-        <v>80392</v>
+        <v>93440</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>229497</v>
+        <v>6047725</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
+          <t>Skog vid Lappbrännbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>550359</v>
+        <v>550558</v>
       </c>
       <c r="R40" t="n">
-        <v>6994564</v>
+        <v>6994443</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4878,17 +4859,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>På asp</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4914,108 +4890,6 @@
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/126098483</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>136674417</v>
-      </c>
-      <c r="B41" t="n">
-        <v>93440</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>6047725</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Rödfläckig zontaggsvamp</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Skog vid Lappbrännbäcken, Jmt</t>
-        </is>
-      </c>
-      <c r="Q41" t="n">
-        <v>550558</v>
-      </c>
-      <c r="R41" t="n">
-        <v>6994443</v>
-      </c>
-      <c r="S41" t="n">
-        <v>10</v>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="AD41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF41" t="inlineStr"/>
-      <c r="AG41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT41" t="inlineStr"/>
-      <c r="AW41" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
-      <c r="AZ41" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136674417</t>
         </is>
@@ -5062,7 +4936,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41415-2024 artfynd.xlsx
+++ b/artfynd/A 41415-2024 artfynd.xlsx
@@ -1456,7 +1456,7 @@
         <v>136674360</v>
       </c>
       <c r="B9" t="n">
-        <v>87515</v>
+        <v>87517</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>136673577</v>
       </c>
       <c r="B10" t="n">
-        <v>93442</v>
+        <v>93444</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>136673646</v>
       </c>
       <c r="B11" t="n">
-        <v>93442</v>
+        <v>93444</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>136626251</v>
       </c>
       <c r="B19" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>136673649</v>
       </c>
       <c r="B20" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>136673613</v>
       </c>
       <c r="B21" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>136674417</v>
       </c>
       <c r="B40" t="n">
-        <v>93440</v>
+        <v>93442</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 41415-2024 artfynd.xlsx
+++ b/artfynd/A 41415-2024 artfynd.xlsx
@@ -1456,7 +1456,7 @@
         <v>136674360</v>
       </c>
       <c r="B9" t="n">
-        <v>87517</v>
+        <v>87530</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>136673577</v>
       </c>
       <c r="B10" t="n">
-        <v>93444</v>
+        <v>93457</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>136673646</v>
       </c>
       <c r="B11" t="n">
-        <v>93444</v>
+        <v>93457</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>136626251</v>
       </c>
       <c r="B19" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>136673649</v>
       </c>
       <c r="B20" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>136673613</v>
       </c>
       <c r="B21" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>136674417</v>
       </c>
       <c r="B40" t="n">
-        <v>93442</v>
+        <v>93455</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 41415-2024 artfynd.xlsx
+++ b/artfynd/A 41415-2024 artfynd.xlsx
@@ -1456,7 +1456,7 @@
         <v>136674360</v>
       </c>
       <c r="B9" t="n">
-        <v>87530</v>
+        <v>87532</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>136673577</v>
       </c>
       <c r="B10" t="n">
-        <v>93457</v>
+        <v>93458</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>136673646</v>
       </c>
       <c r="B11" t="n">
-        <v>93457</v>
+        <v>93458</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>136626251</v>
       </c>
       <c r="B19" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>136673649</v>
       </c>
       <c r="B20" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>136673613</v>
       </c>
       <c r="B21" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>136674417</v>
       </c>
       <c r="B40" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 41415-2024 artfynd.xlsx
+++ b/artfynd/A 41415-2024 artfynd.xlsx
@@ -1456,7 +1456,7 @@
         <v>136674360</v>
       </c>
       <c r="B9" t="n">
-        <v>87532</v>
+        <v>87535</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>136673577</v>
       </c>
       <c r="B10" t="n">
-        <v>93458</v>
+        <v>93461</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>136673646</v>
       </c>
       <c r="B11" t="n">
-        <v>93458</v>
+        <v>93461</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>136626251</v>
       </c>
       <c r="B19" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>136673649</v>
       </c>
       <c r="B20" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>136673613</v>
       </c>
       <c r="B21" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>136674417</v>
       </c>
       <c r="B40" t="n">
-        <v>93456</v>
+        <v>93459</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
